--- a/output/pdf_financials_xlsx/DF.xlsx
+++ b/output/pdf_financials_xlsx/DF.xlsx
@@ -2281,40 +2281,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>7.976712</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>5.955038</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.962566</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>10.451103</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>19.186938</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>13.086531</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>12.457918</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>22.012552</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>21.33662</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>23.954448</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>63.353314</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>59.81005</v>
       </c>
     </row>
     <row r="35">
@@ -2367,40 +2367,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>7.976712</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>5.955038</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.962566</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>10.451103</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>19.186938</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>13.086531</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>12.457918</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>22.012552</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>21.33662</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>23.954448</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>63.353314</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>59.81005</v>
       </c>
     </row>
     <row r="37">
@@ -2913,10 +2913,10 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>375.377869</v>
+        <v>312.024555</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>458.378657</v>
+        <v>398.568607</v>
       </c>
     </row>
     <row r="49">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
